--- a/data/Bambu_Filament_Tracker.xlsx
+++ b/data/Bambu_Filament_Tracker.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,6 +79,7 @@
       <name val="Arial"/>
       <sz val="10"/>
     </font>
+    <font/>
   </fonts>
   <fills count="9">
     <fill>
@@ -123,7 +124,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -159,11 +160,12 @@
         <color rgb="00444444"/>
       </bottom>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -225,6 +227,7 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -609,7 +612,7 @@
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>Last updated: 5/7/26</t>
+          <t>Last updated: 5/10/26</t>
         </is>
       </c>
     </row>
@@ -655,14 +658,14 @@
         <v>30</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -681,14 +684,14 @@
         <v>25</v>
       </c>
       <c r="C4" s="10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -707,14 +710,14 @@
         <v>7</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -733,14 +736,14 @@
         <v>14</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -759,14 +762,14 @@
         <v>6</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -785,14 +788,14 @@
         <v>7</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -813,12 +816,12 @@
       <c r="C9" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -841,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM32"/>
+  <dimension ref="A1:BP32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -909,6 +912,9 @@
     <col width="10" customWidth="1" min="63" max="63"/>
     <col width="10" customWidth="1" min="64" max="64"/>
     <col width="10" customWidth="1" min="65" max="65"/>
+    <col width="12" customWidth="1" min="66" max="66"/>
+    <col width="12" customWidth="1" min="67" max="67"/>
+    <col width="12" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1249,6 +1255,21 @@
           <t>5/7/26</t>
         </is>
       </c>
+      <c r="BN2" s="3" t="inlineStr">
+        <is>
+          <t>5/8/26</t>
+        </is>
+      </c>
+      <c r="BO2" s="3" t="inlineStr">
+        <is>
+          <t>5/9/26</t>
+        </is>
+      </c>
+      <c r="BP2" s="3" t="inlineStr">
+        <is>
+          <t>5/10/26</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
@@ -1574,6 +1595,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN3" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO3" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP3" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="n">
@@ -1899,6 +1935,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN4" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO4" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP4" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
@@ -2224,6 +2275,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN5" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO5" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP5" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="n">
@@ -2549,6 +2615,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN6" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO6" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP6" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
@@ -2874,6 +2955,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN7" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO7" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP7" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="n">
@@ -3199,6 +3295,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN8" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO8" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BP8" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
@@ -3524,6 +3635,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN9" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO9" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP9" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="16" t="n">
@@ -3849,6 +3975,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN10" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO10" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP10" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="n">
@@ -4174,6 +4315,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN11" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO11" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP11" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="16" t="n">
@@ -4499,6 +4655,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN12" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO12" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP12" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="n">
@@ -4824,6 +4995,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN13" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO13" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP13" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="16" t="n">
@@ -5149,6 +5335,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN14" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO14" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP14" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="n">
@@ -5474,6 +5675,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN15" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO15" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP15" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="16" t="n">
@@ -5799,6 +6015,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN16" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO16" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP16" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="n">
@@ -6124,6 +6355,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN17" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO17" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP17" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="16" t="n">
@@ -6449,6 +6695,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN18" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO18" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP18" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="n">
@@ -6774,6 +7035,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN19" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO19" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BP19" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="16" t="n">
@@ -7099,6 +7375,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN20" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO20" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP20" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="n">
@@ -7424,6 +7715,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN21" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO21" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP21" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="16" t="n">
@@ -7749,6 +8055,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN22" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO22" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP22" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="n">
@@ -8074,6 +8395,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN23" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO23" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP23" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="16" t="n">
@@ -8399,6 +8735,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN24" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO24" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP24" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="n">
@@ -8724,6 +9075,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN25" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO25" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP25" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="16" t="n">
@@ -9049,6 +9415,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN26" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO26" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP26" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="n">
@@ -9374,6 +9755,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN27" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO27" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP27" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="16" t="n">
@@ -9699,6 +10095,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN28" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO28" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP28" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="n">
@@ -10024,6 +10435,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN29" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO29" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP29" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="16" t="n">
@@ -10349,6 +10775,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN30" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO30" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP30" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="n">
@@ -10674,6 +11115,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN31" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO31" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP31" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="16" t="n">
@@ -10995,6 +11451,21 @@
         </is>
       </c>
       <c r="BM32" s="20" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BN32" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO32" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP32" s="15" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -11014,7 +11485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM27"/>
+  <dimension ref="A1:BP27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11082,6 +11553,9 @@
     <col width="10" customWidth="1" min="63" max="63"/>
     <col width="10" customWidth="1" min="64" max="64"/>
     <col width="10" customWidth="1" min="65" max="65"/>
+    <col width="12" customWidth="1" min="66" max="66"/>
+    <col width="12" customWidth="1" min="67" max="67"/>
+    <col width="12" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -11422,6 +11896,21 @@
           <t>5/7/26</t>
         </is>
       </c>
+      <c r="BN2" s="3" t="inlineStr">
+        <is>
+          <t>5/8/26</t>
+        </is>
+      </c>
+      <c r="BO2" s="3" t="inlineStr">
+        <is>
+          <t>5/9/26</t>
+        </is>
+      </c>
+      <c r="BP2" s="3" t="inlineStr">
+        <is>
+          <t>5/10/26</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
@@ -11747,6 +12236,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN3" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO3" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP3" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="n">
@@ -12072,6 +12576,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN4" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO4" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP4" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
@@ -12397,6 +12916,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN5" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO5" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP5" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="n">
@@ -12722,6 +13256,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN6" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO6" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BP6" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
@@ -13047,6 +13596,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN7" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO7" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP7" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="n">
@@ -13372,6 +13936,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN8" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO8" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP8" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
@@ -13697,6 +14276,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN9" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO9" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP9" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="16" t="n">
@@ -14022,6 +14616,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN10" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO10" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP10" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="n">
@@ -14347,6 +14956,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN11" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO11" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP11" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="16" t="n">
@@ -14672,6 +15296,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN12" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO12" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP12" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="n">
@@ -14997,6 +15636,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN13" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO13" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP13" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="16" t="n">
@@ -15322,6 +15976,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN14" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO14" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP14" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="n">
@@ -15647,6 +16316,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN15" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO15" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP15" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="16" t="n">
@@ -15972,6 +16656,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN16" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO16" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP16" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="n">
@@ -16297,6 +16996,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN17" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO17" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP17" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="16" t="n">
@@ -16622,6 +17336,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN18" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO18" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BP18" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="n">
@@ -16947,6 +17676,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN19" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO19" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP19" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="16" t="n">
@@ -17272,6 +18016,21 @@
           <t>🚫</t>
         </is>
       </c>
+      <c r="BN20" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO20" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP20" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="n">
@@ -17597,6 +18356,21 @@
           <t>🚫</t>
         </is>
       </c>
+      <c r="BN21" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO21" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP21" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="16" t="n">
@@ -17922,6 +18696,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN22" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO22" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP22" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="n">
@@ -18247,6 +19036,21 @@
           <t>🚫</t>
         </is>
       </c>
+      <c r="BN23" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO23" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BP23" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="16" t="n">
@@ -18572,6 +19376,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN24" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO24" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP24" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="n">
@@ -18897,6 +19716,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN25" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO25" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP25" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="16" t="n">
@@ -19222,6 +20056,16 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BO26" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP26" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="n">
@@ -19543,6 +20387,16 @@
         </is>
       </c>
       <c r="BM27" s="19" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO27" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP27" s="15" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -19562,7 +20416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM9"/>
+  <dimension ref="A1:BP9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -19630,6 +20484,9 @@
     <col width="10" customWidth="1" min="63" max="63"/>
     <col width="10" customWidth="1" min="64" max="64"/>
     <col width="10" customWidth="1" min="65" max="65"/>
+    <col width="12" customWidth="1" min="66" max="66"/>
+    <col width="12" customWidth="1" min="67" max="67"/>
+    <col width="12" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -19970,6 +20827,21 @@
           <t>5/7/26</t>
         </is>
       </c>
+      <c r="BN2" s="3" t="inlineStr">
+        <is>
+          <t>5/8/26</t>
+        </is>
+      </c>
+      <c r="BO2" s="3" t="inlineStr">
+        <is>
+          <t>5/9/26</t>
+        </is>
+      </c>
+      <c r="BP2" s="3" t="inlineStr">
+        <is>
+          <t>5/10/26</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
@@ -20295,6 +21167,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN3" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO3" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP3" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="n">
@@ -20620,6 +21507,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN4" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO4" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP4" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
@@ -20945,6 +21847,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN5" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO5" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP5" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="n">
@@ -21270,6 +22187,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN6" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO6" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP6" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
@@ -21595,6 +22527,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN7" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO7" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP7" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="n">
@@ -21920,6 +22867,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN8" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO8" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP8" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
@@ -22243,6 +23205,21 @@
       <c r="BM9" s="19" t="inlineStr">
         <is>
           <t>🚫</t>
+        </is>
+      </c>
+      <c r="BN9" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO9" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP9" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
@@ -22260,7 +23237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM16"/>
+  <dimension ref="A1:BP16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -22328,6 +23305,9 @@
     <col width="10" customWidth="1" min="63" max="63"/>
     <col width="10" customWidth="1" min="64" max="64"/>
     <col width="10" customWidth="1" min="65" max="65"/>
+    <col width="12" customWidth="1" min="66" max="66"/>
+    <col width="12" customWidth="1" min="67" max="67"/>
+    <col width="12" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -22668,6 +23648,21 @@
           <t>5/7/26</t>
         </is>
       </c>
+      <c r="BN2" s="3" t="inlineStr">
+        <is>
+          <t>5/8/26</t>
+        </is>
+      </c>
+      <c r="BO2" s="3" t="inlineStr">
+        <is>
+          <t>5/9/26</t>
+        </is>
+      </c>
+      <c r="BP2" s="3" t="inlineStr">
+        <is>
+          <t>5/10/26</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
@@ -22993,6 +23988,21 @@
           <t>🚫</t>
         </is>
       </c>
+      <c r="BN3" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO3" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BP3" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="n">
@@ -23318,6 +24328,21 @@
           <t>🚫</t>
         </is>
       </c>
+      <c r="BN4" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO4" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BP4" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
@@ -23643,6 +24668,21 @@
           <t>🚫</t>
         </is>
       </c>
+      <c r="BN5" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO5" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BP5" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="n">
@@ -23968,6 +25008,21 @@
           <t>🚫</t>
         </is>
       </c>
+      <c r="BN6" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO6" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BP6" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
@@ -24293,6 +25348,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN7" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO7" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BP7" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="n">
@@ -24618,6 +25688,21 @@
           <t>🚫</t>
         </is>
       </c>
+      <c r="BN8" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO8" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BP8" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
@@ -24943,6 +26028,21 @@
           <t>🚫</t>
         </is>
       </c>
+      <c r="BN9" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO9" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BP9" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="16" t="n">
@@ -25268,6 +26368,21 @@
           <t>🚫</t>
         </is>
       </c>
+      <c r="BN10" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO10" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BP10" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="n">
@@ -25593,6 +26708,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN11" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO11" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BP11" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="16" t="n">
@@ -25918,6 +27048,21 @@
           <t>🚫</t>
         </is>
       </c>
+      <c r="BN12" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO12" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BP12" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="n">
@@ -26243,6 +27388,21 @@
           <t>🚫</t>
         </is>
       </c>
+      <c r="BN13" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO13" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BP13" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="16" t="n">
@@ -26568,6 +27728,21 @@
           <t>🚫</t>
         </is>
       </c>
+      <c r="BN14" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO14" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BP14" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="n">
@@ -26893,6 +28068,21 @@
           <t>🚫</t>
         </is>
       </c>
+      <c r="BN15" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO15" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BP15" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="16" t="n">
@@ -27214,6 +28404,16 @@
         </is>
       </c>
       <c r="BM16" s="20" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO16" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BP16" s="17" t="inlineStr">
         <is>
           <t>🚫</t>
         </is>
@@ -27233,7 +28433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM8"/>
+  <dimension ref="A1:BP8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -27301,6 +28501,9 @@
     <col width="10" customWidth="1" min="63" max="63"/>
     <col width="10" customWidth="1" min="64" max="64"/>
     <col width="10" customWidth="1" min="65" max="65"/>
+    <col width="12" customWidth="1" min="66" max="66"/>
+    <col width="12" customWidth="1" min="67" max="67"/>
+    <col width="12" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -27641,6 +28844,21 @@
           <t>5/7/26</t>
         </is>
       </c>
+      <c r="BN2" s="3" t="inlineStr">
+        <is>
+          <t>5/8/26</t>
+        </is>
+      </c>
+      <c r="BO2" s="3" t="inlineStr">
+        <is>
+          <t>5/9/26</t>
+        </is>
+      </c>
+      <c r="BP2" s="3" t="inlineStr">
+        <is>
+          <t>5/10/26</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
@@ -27966,6 +29184,21 @@
           <t>🚫</t>
         </is>
       </c>
+      <c r="BN3" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO3" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP3" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="n">
@@ -28291,6 +29524,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN4" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO4" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP4" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
@@ -28616,6 +29864,21 @@
           <t>🚫</t>
         </is>
       </c>
+      <c r="BN5" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO5" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP5" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="n">
@@ -28941,6 +30204,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN6" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO6" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP6" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
@@ -29266,6 +30544,21 @@
           <t>🚫</t>
         </is>
       </c>
+      <c r="BN7" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO7" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP7" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="n">
@@ -29587,6 +30880,21 @@
         </is>
       </c>
       <c r="BM8" s="20" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BN8" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO8" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP8" s="15" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -29606,7 +30914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM9"/>
+  <dimension ref="A1:BP9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -29674,6 +30982,9 @@
     <col width="10" customWidth="1" min="63" max="63"/>
     <col width="10" customWidth="1" min="64" max="64"/>
     <col width="10" customWidth="1" min="65" max="65"/>
+    <col width="12" customWidth="1" min="66" max="66"/>
+    <col width="12" customWidth="1" min="67" max="67"/>
+    <col width="12" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -30014,6 +31325,21 @@
           <t>5/7/26</t>
         </is>
       </c>
+      <c r="BN2" s="3" t="inlineStr">
+        <is>
+          <t>5/8/26</t>
+        </is>
+      </c>
+      <c r="BO2" s="3" t="inlineStr">
+        <is>
+          <t>5/9/26</t>
+        </is>
+      </c>
+      <c r="BP2" s="3" t="inlineStr">
+        <is>
+          <t>5/10/26</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
@@ -30339,6 +31665,21 @@
           <t>🚫</t>
         </is>
       </c>
+      <c r="BN3" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO3" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP3" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="n">
@@ -30664,6 +32005,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN4" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO4" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP4" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
@@ -30989,6 +32345,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN5" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO5" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP5" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="n">
@@ -31314,6 +32685,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN6" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO6" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP6" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
@@ -31639,6 +33025,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN7" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO7" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP7" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="n">
@@ -31964,6 +33365,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN8" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO8" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP8" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
@@ -32285,6 +33701,21 @@
         </is>
       </c>
       <c r="BM9" s="19" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BN9" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO9" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP9" s="15" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -32304,7 +33735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM15"/>
+  <dimension ref="A1:BP26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -32372,6 +33803,9 @@
     <col width="10" customWidth="1" min="63" max="63"/>
     <col width="10" customWidth="1" min="64" max="64"/>
     <col width="10" customWidth="1" min="65" max="65"/>
+    <col width="12" customWidth="1" min="66" max="66"/>
+    <col width="12" customWidth="1" min="67" max="67"/>
+    <col width="12" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -32712,6 +34146,21 @@
           <t>5/7/26</t>
         </is>
       </c>
+      <c r="BN2" s="3" t="inlineStr">
+        <is>
+          <t>5/8/26</t>
+        </is>
+      </c>
+      <c r="BO2" s="3" t="inlineStr">
+        <is>
+          <t>5/9/26</t>
+        </is>
+      </c>
+      <c r="BP2" s="3" t="inlineStr">
+        <is>
+          <t>5/10/26</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="14" t="n">
@@ -33037,6 +34486,21 @@
           <t>🚫</t>
         </is>
       </c>
+      <c r="BN3" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO3" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BP3" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="n">
@@ -33362,6 +34826,21 @@
           <t>🚫</t>
         </is>
       </c>
+      <c r="BN4" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO4" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP4" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="n">
@@ -33687,6 +35166,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN5" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO5" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP5" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="n">
@@ -34012,6 +35506,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN6" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO6" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP6" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="n">
@@ -34337,6 +35846,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN7" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO7" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP7" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="n">
@@ -34662,6 +36186,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN8" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO8" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP8" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n">
@@ -34987,6 +36526,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN9" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO9" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP9" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="16" t="n">
@@ -35312,6 +36866,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN10" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO10" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP10" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="n">
@@ -35637,6 +37206,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN11" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO11" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP11" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="16" t="n">
@@ -35962,6 +37546,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN12" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO12" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP12" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="n">
@@ -36287,6 +37886,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN13" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO13" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP13" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="16" t="n">
@@ -36612,6 +38226,21 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN14" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO14" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP14" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="n">
@@ -36937,6 +38566,159 @@
           <t>✅</t>
         </is>
       </c>
+      <c r="BN15" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO15" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP15" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="BN16" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO16" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP16" s="21" t="n"/>
+    </row>
+    <row r="17">
+      <c r="BN17" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO17" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP17" s="21" t="n"/>
+    </row>
+    <row r="18">
+      <c r="BN18" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO18" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP18" s="21" t="n"/>
+    </row>
+    <row r="19">
+      <c r="BN19" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO19" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP19" s="21" t="n"/>
+    </row>
+    <row r="20">
+      <c r="BN20" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO20" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP20" s="21" t="n"/>
+    </row>
+    <row r="21">
+      <c r="BN21" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO21" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP21" s="21" t="n"/>
+    </row>
+    <row r="22">
+      <c r="BN22" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO22" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP22" s="21" t="n"/>
+    </row>
+    <row r="23">
+      <c r="BN23" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO23" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BP23" s="21" t="n"/>
+    </row>
+    <row r="24">
+      <c r="BN24" s="17" t="inlineStr">
+        <is>
+          <t>🚫</t>
+        </is>
+      </c>
+      <c r="BO24" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP24" s="21" t="n"/>
+    </row>
+    <row r="25">
+      <c r="BN25" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BO25" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP25" s="21" t="n"/>
+    </row>
+    <row r="26">
+      <c r="BO26" s="15" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="BP26" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
